--- a/resources/templates/standard/A3200-02.xlsx
+++ b/resources/templates/standard/A3200-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>이해 관계자 불만 조치일지</t>
   </si>
@@ -525,12 +528,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -553,7 +558,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
       <c r="Z1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA1" s="3"/>
       <c r="AB1" s="3"/>
@@ -662,7 +667,7 @@
     </row>
     <row r="5" ht="35.1" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -679,7 +684,7 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -714,7 +719,7 @@
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
       <c r="P6" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
@@ -749,7 +754,7 @@
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
       <c r="P7" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
@@ -769,7 +774,7 @@
     </row>
     <row r="8" ht="35.1" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -786,7 +791,7 @@
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
       <c r="P8" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
@@ -905,7 +910,7 @@
     </row>
     <row r="12" ht="35.1" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -1238,37 +1243,37 @@
     <row r="22" ht="20.1" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
       <c r="J22" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
       <c r="M22" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N22" s="9"/>
       <c r="O22" s="9"/>
       <c r="P22" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
       <c r="S22" s="5"/>
       <c r="T22" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U22" s="11"/>
       <c r="V22" s="9"/>
